--- a/data/Item.xlsx
+++ b/data/Item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,11 @@
           <t>max_stack_size</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>equip_kind</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +444,11 @@
           <t>uint32</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>uint32</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,19 +461,33 @@
           <t>common</t>
         </is>
       </c>
-    </row>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
           <t>最大堆叠数量</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>装备部位:0=不是装备。&gt;0=该部位编号。部位的含义(手镯/头/胸…)以及每个部位有几个槽,全部由数据定义 —— 槽位表 EquipSlot 决定哪个槽接受哪个部位,代码里不写死</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>1</v>
       </c>
       <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -474,6 +498,9 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -482,6 +509,9 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -490,6 +520,9 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -498,6 +531,9 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -506,6 +542,9 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -514,6 +553,9 @@
       <c r="B12" t="n">
         <v>1</v>
       </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -522,6 +564,9 @@
       <c r="B13" t="n">
         <v>1</v>
       </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -530,6 +575,9 @@
       <c r="B14" t="n">
         <v>2</v>
       </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -538,6 +586,9 @@
       <c r="B15" t="n">
         <v>999</v>
       </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -546,6 +597,9 @@
       <c r="B16" t="n">
         <v>999</v>
       </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -554,6 +608,9 @@
       <c r="B17" t="n">
         <v>1</v>
       </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -562,6 +619,9 @@
       <c r="B18" t="n">
         <v>1</v>
       </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -570,6 +630,9 @@
       <c r="B19" t="n">
         <v>1</v>
       </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -578,6 +641,9 @@
       <c r="B20" t="n">
         <v>999</v>
       </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -586,6 +652,9 @@
       <c r="B21" t="n">
         <v>999</v>
       </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -594,6 +663,9 @@
       <c r="B22" t="n">
         <v>999</v>
       </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -602,6 +674,9 @@
       <c r="B23" t="n">
         <v>999</v>
       </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -610,6 +685,9 @@
       <c r="B24" t="n">
         <v>999</v>
       </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -618,6 +696,9 @@
       <c r="B25" t="n">
         <v>999</v>
       </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -626,6 +707,9 @@
       <c r="B26" t="n">
         <v>999</v>
       </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -634,6 +718,9 @@
       <c r="B27" t="n">
         <v>999</v>
       </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -642,6 +729,9 @@
       <c r="B28" t="n">
         <v>999</v>
       </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -650,6 +740,9 @@
       <c r="B29" t="n">
         <v>999</v>
       </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -658,6 +751,9 @@
       <c r="B30" t="n">
         <v>999</v>
       </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -666,6 +762,9 @@
       <c r="B31" t="n">
         <v>999</v>
       </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -674,6 +773,9 @@
       <c r="B32" t="n">
         <v>999</v>
       </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -681,6 +783,9 @@
       </c>
       <c r="B33" t="n">
         <v>999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/Item.xlsx
+++ b/data/Item.xlsx
@@ -433,40 +433,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4"/>
     <row r="5">
       <c r="B5" t="inlineStr">
